--- a/data/trans_dic/P1409-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1409-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,86</t>
+          <t>1,71; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,99</t>
+          <t>2,2; 6,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,64</t>
+          <t>2,63; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,01</t>
+          <t>1,57; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,8</t>
+          <t>3,48; 7,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,46</t>
+          <t>0,77; 5,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,33</t>
+          <t>2,04; 4,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,12</t>
+          <t>3,36; 6,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,8</t>
+          <t>2,26; 6,94</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,33</t>
+          <t>1,17; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,2</t>
+          <t>1,55; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,35</t>
+          <t>3,7; 9,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,46</t>
+          <t>2,27; 5,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,65</t>
+          <t>2,39; 5,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 50,92</t>
+          <t>2,69; 6,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,85</t>
+          <t>1,94; 3,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,35</t>
+          <t>2,31; 4,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 33,51</t>
+          <t>3,76; 6,95</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,45</t>
+          <t>0,62; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,45</t>
+          <t>0,95; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,3</t>
+          <t>2,38; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,95</t>
+          <t>1,4; 3,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,07</t>
+          <t>2,27; 5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,63</t>
+          <t>3,25; 6,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,75</t>
+          <t>1,18; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,64</t>
+          <t>1,85; 3,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,7</t>
+          <t>3,17; 5,27</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,58</t>
+          <t>0,33; 2,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,49</t>
+          <t>0,6; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,79</t>
+          <t>1,88; 4,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,43</t>
+          <t>0,81; 3,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,09</t>
+          <t>2,1; 5,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,14</t>
+          <t>4,41; 7,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,47</t>
+          <t>0,78; 2,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,4</t>
+          <t>1,47; 3,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,76</t>
+          <t>3,49; 5,35</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,91</t>
+          <t>0,48; 2,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,49</t>
+          <t>1,16; 4,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,37</t>
+          <t>1,63; 4,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,04</t>
+          <t>1,6; 5,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,24</t>
+          <t>2,25; 6,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,9</t>
+          <t>3,43; 6,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,27</t>
+          <t>1,3; 3,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,52</t>
+          <t>2,17; 4,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,63</t>
+          <t>2,81; 4,69</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,07</t>
+          <t>1,61; 6,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,52</t>
+          <t>0,6; 3,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,61</t>
+          <t>1,64; 4,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,67</t>
+          <t>1,11; 4,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,43</t>
+          <t>2,39; 6,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,12</t>
+          <t>3,52; 6,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,5</t>
+          <t>1,75; 4,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,26</t>
+          <t>1,79; 4,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,25</t>
+          <t>2,95; 4,96</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,5</t>
+          <t>1,28; 6,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,09</t>
+          <t>3,63; 9,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,15</t>
+          <t>1,77; 5,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,25</t>
+          <t>1,42; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,79</t>
+          <t>2,85; 7,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,03</t>
+          <t>4,82; 8,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,58</t>
+          <t>1,87; 4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,61</t>
+          <t>3,61; 7,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,31</t>
+          <t>3,97; 6,27</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,48</t>
+          <t>1,48; 2,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,13</t>
+          <t>2,02; 3,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,61</t>
+          <t>3,16; 4,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,37</t>
+          <t>2,19; 3,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,69</t>
+          <t>3,38; 4,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,9</t>
+          <t>4,25; 5,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,73</t>
+          <t>2,0; 2,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,75</t>
+          <t>2,86; 3,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,73</t>
+          <t>3,88; 4,82</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>32693</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7640; 22078</t>
+          <t>7754; 21301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10241; 25134</t>
+          <t>9220; 25256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9335; 46551</t>
+          <t>10723; 44549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6783; 21537</t>
+          <t>6765; 20364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13464; 30860</t>
+          <t>13780; 30607</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2249; 17098</t>
+          <t>2787; 20239</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17647; 38273</t>
+          <t>18031; 37068</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26782; 49888</t>
+          <t>27415; 49964</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14704; 55622</t>
+          <t>17425; 53428</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87116</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>49978</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7952; 22852</t>
+          <t>8059; 23187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8895; 24820</t>
+          <t>9149; 24274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18280; 43841</t>
+          <t>17645; 45467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14435; 33315</t>
+          <t>13841; 33164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14139; 31867</t>
+          <t>13454; 31691</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17351; 260441</t>
+          <t>13466; 31191</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24973; 49996</t>
+          <t>25187; 48353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26508; 50194</t>
+          <t>26675; 50374</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45158; 313305</t>
+          <t>36761; 67936</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>52286</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4640; 16718</t>
+          <t>4211; 16691</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6648; 23099</t>
+          <t>6342; 21648</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13176; 33724</t>
+          <t>14737; 35079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10061; 28024</t>
+          <t>9934; 27691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14166; 33512</t>
+          <t>14988; 33431</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19037; 35947</t>
+          <t>20197; 38366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17264; 38210</t>
+          <t>16351; 37834</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25443; 48419</t>
+          <t>24613; 49528</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35286; 61418</t>
+          <t>39389; 65396</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>62887</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2167; 15881</t>
+          <t>2029; 14883</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3195; 16072</t>
+          <t>3874; 16966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8631; 33679</t>
+          <t>13170; 32423</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4639; 21059</t>
+          <t>4978; 21414</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13472; 33034</t>
+          <t>13626; 32706</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29499; 50843</t>
+          <t>32429; 52967</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9802; 30328</t>
+          <t>9535; 28032</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20017; 44048</t>
+          <t>19091; 42565</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35563; 76174</t>
+          <t>50182; 76838</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>44189</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2096; 12493</t>
+          <t>2044; 10631</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5952; 21468</t>
+          <t>5535; 22013</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9063; 24467</t>
+          <t>9901; 26764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7216; 22580</t>
+          <t>7145; 23121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11661; 30979</t>
+          <t>11194; 30088</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18489; 32104</t>
+          <t>20759; 36892</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10694; 28697</t>
+          <t>11385; 29610</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21181; 44041</t>
+          <t>21154; 45068</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30556; 51079</t>
+          <t>34094; 56944</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>32757</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4659; 18790</t>
+          <t>4990; 19619</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2001; 11765</t>
+          <t>2006; 11981</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6642; 16939</t>
+          <t>6671; 18599</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4811; 16519</t>
+          <t>3936; 16339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9116; 24305</t>
+          <t>9034; 24051</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6563; 31066</t>
+          <t>15440; 28917</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11860; 29867</t>
+          <t>11606; 29943</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12470; 30353</t>
+          <t>12745; 31278</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13117; 41455</t>
+          <t>24931; 41890</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26828</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>38788</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3137; 13743</t>
+          <t>3188; 15916</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9274; 23362</t>
+          <t>9336; 23702</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5204; 14572</t>
+          <t>5486; 16160</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6417; 20357</t>
+          <t>5508; 19983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10297; 31155</t>
+          <t>11416; 31511</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20256; 34166</t>
+          <t>22372; 38520</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11701; 29231</t>
+          <t>11923; 29104</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23765; 50003</t>
+          <t>23737; 47244</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28047; 44658</t>
+          <t>30760; 48519</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51408; 84834</t>
+          <t>50578; 83690</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68851; 106386</t>
+          <t>68484; 106829</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95309; 159198</t>
+          <t>111411; 165220</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>78185; 119660</t>
+          <t>77982; 119290</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>119238; 166235</t>
+          <t>119676; 166461</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>152418; 508248</t>
+          <t>158583; 200886</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>139010; 190369</t>
+          <t>139304; 190443</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>200126; 260204</t>
+          <t>198200; 259201</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>273464; 620534</t>
+          <t>281706; 349650</t>
         </is>
       </c>
     </row>
